--- a/data/trans_orig/P35-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P35-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2007</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2007 (tasa de respuesta: 95,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103230</t>
+          <t>100614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>141359</t>
+          <t>139452</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124990</t>
+          <t>126630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>168653</t>
+          <t>167011</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>239457</t>
+          <t>241582</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>295093</t>
+          <t>299653</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>520004</t>
+          <t>521911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>558133</t>
+          <t>560749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>485796</t>
+          <t>487438</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>529459</t>
+          <t>527819</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1020719</t>
+          <t>1016159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1076355</t>
+          <t>1074230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126108</t>
+          <t>125717</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>171828</t>
+          <t>168559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190091</t>
+          <t>190691</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>241998</t>
+          <t>242923</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>329586</t>
+          <t>330362</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>400115</t>
+          <t>399613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>754865</t>
+          <t>758134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>800585</t>
+          <t>800976</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>682191</t>
+          <t>681266</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>734098</t>
+          <t>733498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1450767</t>
+          <t>1451269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1521296</t>
+          <t>1520520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106349</t>
+          <t>107873</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149650</t>
+          <t>148645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>143280</t>
+          <t>140953</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185433</t>
+          <t>183550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260076</t>
+          <t>256570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>319488</t>
+          <t>318583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>482959</t>
+          <t>483964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526260</t>
+          <t>524736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449043</t>
+          <t>450926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>491196</t>
+          <t>493523</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>947597</t>
+          <t>948502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1007009</t>
+          <t>1010515</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131194</t>
+          <t>132427</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174240</t>
+          <t>175576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145880</t>
+          <t>144356</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193819</t>
+          <t>190687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>288517</t>
+          <t>289981</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>351302</t>
+          <t>354799</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>732318</t>
+          <t>730982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>775364</t>
+          <t>774131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>801100</t>
+          <t>804232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>849039</t>
+          <t>850563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1550175</t>
+          <t>1546678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1612960</t>
+          <t>1611496</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>504055</t>
+          <t>510422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>589433</t>
+          <t>590682</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>643049</t>
+          <t>645355</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>737446</t>
+          <t>734471</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1182969</t>
+          <t>1178787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1304283</t>
+          <t>1297968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2537790</t>
+          <t>2536541</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2623168</t>
+          <t>2616801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2470587</t>
+          <t>2473562</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2564984</t>
+          <t>2562678</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5030973</t>
+          <t>5037288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5152287</t>
+          <t>5156469</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,39%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2012</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2012 (tasa de respuesta: 97,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146878</t>
+          <t>145228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>193770</t>
+          <t>192634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191368</t>
+          <t>192346</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238942</t>
+          <t>243135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>349309</t>
+          <t>350956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>419754</t>
+          <t>419971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>499367</t>
+          <t>500503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>546259</t>
+          <t>547909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>436354</t>
+          <t>432161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>483928</t>
+          <t>482950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>948679</t>
+          <t>948462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1019124</t>
+          <t>1017477</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,35%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>232380</t>
+          <t>232143</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>289130</t>
+          <t>287322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>320476</t>
+          <t>322233</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>382748</t>
+          <t>380147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>566162</t>
+          <t>565681</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>655607</t>
+          <t>652118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>707294</t>
+          <t>709102</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>764044</t>
+          <t>764281</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>624788</t>
+          <t>627389</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>687060</t>
+          <t>685303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1348353</t>
+          <t>1351842</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1437798</t>
+          <t>1438279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171237</t>
+          <t>172345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>223323</t>
+          <t>223848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>239714</t>
+          <t>240318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>295231</t>
+          <t>293356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>425572</t>
+          <t>422734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>500156</t>
+          <t>501113</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519080</t>
+          <t>518555</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>571166</t>
+          <t>570058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>465299</t>
+          <t>467174</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>520816</t>
+          <t>520212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1002777</t>
+          <t>1001820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1077361</t>
+          <t>1080199</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>215432</t>
+          <t>211638</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>269874</t>
+          <t>267634</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>322205</t>
+          <t>319866</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382861</t>
+          <t>380898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>553096</t>
+          <t>557258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>636832</t>
+          <t>638471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625696</t>
+          <t>627936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>680138</t>
+          <t>683932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>625892</t>
+          <t>627855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>686548</t>
+          <t>688887</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1267490</t>
+          <t>1265851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1351226</t>
+          <t>1347064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,74%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>808315</t>
+          <t>808044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>918082</t>
+          <t>923851</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1128156</t>
+          <t>1128096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1243553</t>
+          <t>1245567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1976645</t>
+          <t>1982308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2138551</t>
+          <t>2128182</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2409452</t>
+          <t>2403683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2519219</t>
+          <t>2519490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2208561</t>
+          <t>2206547</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2323958</t>
+          <t>2324018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4641097</t>
+          <t>4651466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4803003</t>
+          <t>4797340</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2016</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2016 (tasa de respuesta: 98,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>125040</t>
+          <t>123510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>170517</t>
+          <t>166879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>180752</t>
+          <t>181425</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228100</t>
+          <t>230166</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>318559</t>
+          <t>318903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>383164</t>
+          <t>384241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495019</t>
+          <t>498657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>540496</t>
+          <t>542026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>440449</t>
+          <t>438383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>487797</t>
+          <t>487124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>950922</t>
+          <t>949845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1015527</t>
+          <t>1015183</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>261517</t>
+          <t>261377</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>320593</t>
+          <t>321685</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>353103</t>
+          <t>352373</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>416706</t>
+          <t>416981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>628223</t>
+          <t>631463</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>716901</t>
+          <t>718663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>692362</t>
+          <t>691270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>751438</t>
+          <t>751578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>610253</t>
+          <t>609978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>673856</t>
+          <t>674586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1323013</t>
+          <t>1321251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1411691</t>
+          <t>1408451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>217963</t>
+          <t>219053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>272595</t>
+          <t>272337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>260847</t>
+          <t>263072</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>316392</t>
+          <t>315496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>498480</t>
+          <t>498215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>574743</t>
+          <t>571716</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>481557</t>
+          <t>481815</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536189</t>
+          <t>535099</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>454453</t>
+          <t>455349</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>509998</t>
+          <t>507773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>950255</t>
+          <t>953282</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1026518</t>
+          <t>1026783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,33%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>224872</t>
+          <t>221788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>275627</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>308595</t>
+          <t>311130</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>372618</t>
+          <t>372799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>549086</t>
+          <t>551009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>634618</t>
+          <t>635874</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631250</t>
+          <t>629739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>682005</t>
+          <t>685089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>656978</t>
+          <t>656797</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>721001</t>
+          <t>718466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1301854</t>
+          <t>1300598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1387386</t>
+          <t>1385463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,55%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>874749</t>
+          <t>878132</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>984567</t>
+          <t>981053</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1157730</t>
+          <t>1148481</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1281273</t>
+          <t>1268184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2070915</t>
+          <t>2071546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2231270</t>
+          <t>2225499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2354953</t>
+          <t>2358467</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2464771</t>
+          <t>2461388</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2214676</t>
+          <t>2227765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2338219</t>
+          <t>2347468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4604199</t>
+          <t>4609970</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4764554</t>
+          <t>4763923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2023</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>182075</t>
+          <t>182524</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>228989</t>
+          <t>228492</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>212039</t>
+          <t>211785</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>251568</t>
+          <t>250440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>405783</t>
+          <t>399178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>468121</t>
+          <t>464160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406452</t>
+          <t>406949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453366</t>
+          <t>452917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423050</t>
+          <t>424178</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>462579</t>
+          <t>462833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>841939</t>
+          <t>845900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>904277</t>
+          <t>910882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176016</t>
+          <t>150278</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>424423</t>
+          <t>425787</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>370281</t>
+          <t>364587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>420338</t>
+          <t>419117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>488248</t>
+          <t>483796</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>824769</t>
+          <t>823298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,29%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>768441</t>
+          <t>767077</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1016848</t>
+          <t>1042586</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>537226</t>
+          <t>538447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>587283</t>
+          <t>592977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1325659</t>
+          <t>1327130</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1662180</t>
+          <t>1666632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>205945</t>
+          <t>207512</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>261955</t>
+          <t>262626</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130192</t>
+          <t>124755</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>338913</t>
+          <t>334215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>309573</t>
+          <t>329535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>575267</t>
+          <t>570658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>442725</t>
+          <t>442054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>498735</t>
+          <t>497168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>593722</t>
+          <t>598420</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>802443</t>
+          <t>807880</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1062049</t>
+          <t>1066658</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327743</t>
+          <t>1307781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>296073</t>
+          <t>298450</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>355752</t>
+          <t>355895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>311008</t>
+          <t>309630</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>423941</t>
+          <t>425833</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>629343</t>
+          <t>627278</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>764122</t>
+          <t>761852</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>571079</t>
+          <t>570936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>630758</t>
+          <t>628381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>667360</t>
+          <t>665468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>780293</t>
+          <t>781671</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1254011</t>
+          <t>1256281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1388790</t>
+          <t>1390855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>862249</t>
+          <t>843324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1204823</t>
+          <t>1198696</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1043356</t>
+          <t>1005768</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1361965</t>
+          <t>1371118</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2032995</t>
+          <t>2048831</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2509442</t>
+          <t>2530350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2254994</t>
+          <t>2261121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2597568</t>
+          <t>2616493</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2294154</t>
+          <t>2285001</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2612763</t>
+          <t>2650351</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4606494</t>
+          <t>4585586</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5082941</t>
+          <t>5067105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P35-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100614</t>
+          <t>100699</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>139452</t>
+          <t>138785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126630</t>
+          <t>125948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167011</t>
+          <t>167833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>241582</t>
+          <t>234725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>299653</t>
+          <t>294106</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>521911</t>
+          <t>522578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>560749</t>
+          <t>560664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>487438</t>
+          <t>486616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>527819</t>
+          <t>528501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1016159</t>
+          <t>1021706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1074230</t>
+          <t>1081087</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125717</t>
+          <t>125643</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168559</t>
+          <t>170982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190691</t>
+          <t>190170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>242923</t>
+          <t>243987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>330362</t>
+          <t>326418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>399613</t>
+          <t>397773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>758134</t>
+          <t>755711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>800976</t>
+          <t>801050</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>681266</t>
+          <t>680202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>733498</t>
+          <t>734019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1451269</t>
+          <t>1453109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1520520</t>
+          <t>1524464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107873</t>
+          <t>108514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148645</t>
+          <t>151320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140953</t>
+          <t>141476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183550</t>
+          <t>183041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256570</t>
+          <t>260637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318583</t>
+          <t>319005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>483964</t>
+          <t>481289</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524736</t>
+          <t>524095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>450926</t>
+          <t>451435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>493523</t>
+          <t>493000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>948502</t>
+          <t>948080</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1010515</t>
+          <t>1006448</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132427</t>
+          <t>133893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175576</t>
+          <t>174487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>144356</t>
+          <t>145514</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>190687</t>
+          <t>193330</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>289981</t>
+          <t>288945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>354799</t>
+          <t>352337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>730982</t>
+          <t>732071</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>774131</t>
+          <t>772665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>804232</t>
+          <t>801589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>850563</t>
+          <t>849405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1546678</t>
+          <t>1549140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1611496</t>
+          <t>1612532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,8%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>510422</t>
+          <t>508961</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>590682</t>
+          <t>587680</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>645355</t>
+          <t>647402</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>734471</t>
+          <t>744599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1178787</t>
+          <t>1179306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1297968</t>
+          <t>1298809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2536541</t>
+          <t>2539543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2616801</t>
+          <t>2618262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2473562</t>
+          <t>2463434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2562678</t>
+          <t>2560631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5037288</t>
+          <t>5036447</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5156469</t>
+          <t>5155950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145228</t>
+          <t>145232</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>192634</t>
+          <t>192748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>192346</t>
+          <t>191816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243135</t>
+          <t>243101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>350956</t>
+          <t>350138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>419971</t>
+          <t>416870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>500503</t>
+          <t>500389</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>547909</t>
+          <t>547905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>432161</t>
+          <t>432195</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>482950</t>
+          <t>483480</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>948462</t>
+          <t>951563</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1017477</t>
+          <t>1018295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>232143</t>
+          <t>232315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>287322</t>
+          <t>288946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>322233</t>
+          <t>320674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>380147</t>
+          <t>382929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>565681</t>
+          <t>566960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>652118</t>
+          <t>650141</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>709102</t>
+          <t>707478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>764281</t>
+          <t>764109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>627389</t>
+          <t>624607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>685303</t>
+          <t>686862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1351842</t>
+          <t>1353819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1438279</t>
+          <t>1437000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172345</t>
+          <t>168370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>223848</t>
+          <t>223279</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240318</t>
+          <t>241050</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>293356</t>
+          <t>296827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>422734</t>
+          <t>427574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>501113</t>
+          <t>501937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518555</t>
+          <t>519124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>570058</t>
+          <t>574033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>467174</t>
+          <t>463703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>520212</t>
+          <t>519480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1001820</t>
+          <t>1000996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1080199</t>
+          <t>1075359</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,55%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211638</t>
+          <t>213414</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>267634</t>
+          <t>271762</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>319866</t>
+          <t>321476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>380898</t>
+          <t>381596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>557258</t>
+          <t>552342</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>638471</t>
+          <t>640583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>627936</t>
+          <t>623808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>683932</t>
+          <t>682156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>627855</t>
+          <t>627157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>688887</t>
+          <t>687277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1265851</t>
+          <t>1263739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1347064</t>
+          <t>1351980</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>808044</t>
+          <t>808272</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>923851</t>
+          <t>912678</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1128096</t>
+          <t>1132348</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1245567</t>
+          <t>1251401</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1982308</t>
+          <t>1977435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2128182</t>
+          <t>2130614</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2403683</t>
+          <t>2414856</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2519490</t>
+          <t>2519262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2206547</t>
+          <t>2200713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2324018</t>
+          <t>2319766</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4651466</t>
+          <t>4649034</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4797340</t>
+          <t>4802213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123510</t>
+          <t>125222</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166879</t>
+          <t>169050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>181425</t>
+          <t>180910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230166</t>
+          <t>228636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>318903</t>
+          <t>319876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>384241</t>
+          <t>382581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>498657</t>
+          <t>496486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>542026</t>
+          <t>540314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>438383</t>
+          <t>439913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>487124</t>
+          <t>487639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>949845</t>
+          <t>951505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1015183</t>
+          <t>1014210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,02%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>261377</t>
+          <t>257510</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>321685</t>
+          <t>314766</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>352373</t>
+          <t>351696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>416981</t>
+          <t>416080</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>631463</t>
+          <t>632376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>718663</t>
+          <t>719371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>691270</t>
+          <t>698189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>751578</t>
+          <t>755445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>609978</t>
+          <t>610879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>674586</t>
+          <t>675263</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1321251</t>
+          <t>1320543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1408451</t>
+          <t>1407538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,0%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>219053</t>
+          <t>218148</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>272337</t>
+          <t>272623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>263072</t>
+          <t>260523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>315496</t>
+          <t>315629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>498215</t>
+          <t>497237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>571716</t>
+          <t>573858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>481815</t>
+          <t>481529</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535099</t>
+          <t>536004</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455349</t>
+          <t>455216</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>507773</t>
+          <t>510322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>953282</t>
+          <t>951140</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1026783</t>
+          <t>1027761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>221788</t>
+          <t>224021</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>277138</t>
+          <t>276796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>311130</t>
+          <t>307437</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>372799</t>
+          <t>369479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>551009</t>
+          <t>545634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>635874</t>
+          <t>631977</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629739</t>
+          <t>630081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>685089</t>
+          <t>682856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>656797</t>
+          <t>660117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>718466</t>
+          <t>722159</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1300598</t>
+          <t>1304495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1385463</t>
+          <t>1390838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,82%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>878132</t>
+          <t>879891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>981053</t>
+          <t>986707</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1148481</t>
+          <t>1163670</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1268184</t>
+          <t>1273608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2071546</t>
+          <t>2076240</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2225499</t>
+          <t>2232777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2358467</t>
+          <t>2352813</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2461388</t>
+          <t>2459629</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2227765</t>
+          <t>2222341</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2347468</t>
+          <t>2332279</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4609970</t>
+          <t>4602692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4763923</t>
+          <t>4759229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>204817</t>
+          <t>223021</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>182524</t>
+          <t>199609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>228492</t>
+          <t>248763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>231123</t>
+          <t>251905</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>211785</t>
+          <t>231128</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250440</t>
+          <t>274579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>435941</t>
+          <t>474926</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>399178</t>
+          <t>443292</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>464160</t>
+          <t>508272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>430624</t>
+          <t>467689</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406949</t>
+          <t>441947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452917</t>
+          <t>491101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>443495</t>
+          <t>480046</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424178</t>
+          <t>457372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>462833</t>
+          <t>500823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>874119</t>
+          <t>947735</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>845900</t>
+          <t>914389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>910882</t>
+          <t>979369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>68,84%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674618</t>
+          <t>731951</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674618</t>
+          <t>731951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674618</t>
+          <t>731951</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310060</t>
+          <t>1422661</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310060</t>
+          <t>1422661</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310060</t>
+          <t>1422661</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>325731</t>
+          <t>367521</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150278</t>
+          <t>334749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>425787</t>
+          <t>404757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>392567</t>
+          <t>437140</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>364587</t>
+          <t>409528</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>419117</t>
+          <t>467738</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>718298</t>
+          <t>804661</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>483796</t>
+          <t>762881</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>823298</t>
+          <t>853441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>867133</t>
+          <t>681396</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>767077</t>
+          <t>644160</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1042586</t>
+          <t>714168</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>564997</t>
+          <t>633086</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>538447</t>
+          <t>602488</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>592977</t>
+          <t>660698</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1432130</t>
+          <t>1314482</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1327130</t>
+          <t>1265702</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1666632</t>
+          <t>1356262</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957564</t>
+          <t>1070226</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957564</t>
+          <t>1070226</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957564</t>
+          <t>1070226</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150428</t>
+          <t>2119143</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150428</t>
+          <t>2119143</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150428</t>
+          <t>2119143</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>234359</t>
+          <t>266300</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>207512</t>
+          <t>235203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>262626</t>
+          <t>298684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>252674</t>
+          <t>294577</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124755</t>
+          <t>267913</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>334215</t>
+          <t>319663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>487033</t>
+          <t>560877</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>329535</t>
+          <t>523046</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>570658</t>
+          <t>602281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>470321</t>
+          <t>536773</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>442054</t>
+          <t>504389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>497168</t>
+          <t>567870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>679961</t>
+          <t>516959</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>598420</t>
+          <t>491873</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>807880</t>
+          <t>543623</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1150283</t>
+          <t>1053732</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1066658</t>
+          <t>1012328</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1307781</t>
+          <t>1091563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932635</t>
+          <t>811536</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932635</t>
+          <t>811536</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932635</t>
+          <t>811536</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637316</t>
+          <t>1614609</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637316</t>
+          <t>1614609</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637316</t>
+          <t>1614609</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>326756</t>
+          <t>357729</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>298450</t>
+          <t>327838</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>355895</t>
+          <t>388268</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>387269</t>
+          <t>429489</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>309630</t>
+          <t>403453</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>425833</t>
+          <t>458595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>714025</t>
+          <t>787219</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>627278</t>
+          <t>736633</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>761852</t>
+          <t>830514</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>600075</t>
+          <t>632333</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>570936</t>
+          <t>601794</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>628381</t>
+          <t>662224</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>704032</t>
+          <t>687481</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>665468</t>
+          <t>658375</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>781671</t>
+          <t>713517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1304108</t>
+          <t>1319813</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1256281</t>
+          <t>1276518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1390855</t>
+          <t>1370399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>65,04%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091301</t>
+          <t>1116970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091301</t>
+          <t>1116970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091301</t>
+          <t>1116970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018133</t>
+          <t>2107032</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018133</t>
+          <t>2107032</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018133</t>
+          <t>2107032</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1091663</t>
+          <t>1214570</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>843324</t>
+          <t>1154652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1198696</t>
+          <t>1279714</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1263634</t>
+          <t>1413111</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1005768</t>
+          <t>1363945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1371118</t>
+          <t>1468276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2355296</t>
+          <t>2627681</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2048831</t>
+          <t>2555255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2530350</t>
+          <t>2717022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2368154</t>
+          <t>2318192</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2261121</t>
+          <t>2253048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2616493</t>
+          <t>2378110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2392485</t>
+          <t>2317572</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2285001</t>
+          <t>2262407</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2650351</t>
+          <t>2366738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4760640</t>
+          <t>4635764</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4585586</t>
+          <t>4546423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5067105</t>
+          <t>4708190</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
